--- a/hira_material_automation/output/monthly/202601_202609__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__nonmetal_anchor__040019__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-04T22:53:56</t>
+          <t>2026-09-14T23:45:31</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41a0f596b4de9364ee097db1424dddca6a39d075480cf847bd4d1d0d0580eae1</t>
+          <t>bf2c8ad1555eb03ae04ea8f4681fe0a0aca53985c24a1467a2fd960e223bbd01</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202609__nonmetal_anchor__040019__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202609__nonmetal_anchor__040019__normalized.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-14T23:45:31</t>
+          <t>2026-09-24T23:48:53</t>
         </is>
       </c>
     </row>
@@ -797,7 +797,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bf2c8ad1555eb03ae04ea8f4681fe0a0aca53985c24a1467a2fd960e223bbd01</t>
+          <t>c8a5f3d6b9b6845e7b27da13056558ac5638a9963a9f0dba1d78822ed6e25b3f</t>
         </is>
       </c>
     </row>
